--- a/appendix/Experimental_Data.xlsx
+++ b/appendix/Experimental_Data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wlg2o\Documents\景艺大\毕业设计\毕设\4-GraDefense\gradefense\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wlg2o\Documents\景艺大\毕业设计\毕设\4-GraDefense\gradefense\appendix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{293C3266-1487-4522-8FE1-E2F70B96F9E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF513012-5684-4E2F-954B-0F0A96EA2DC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
